--- a/Thesis_TSSP_NEW_M2_Results_3_Scenarios.xlsx
+++ b/Thesis_TSSP_NEW_M2_Results_3_Scenarios.xlsx
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13.4420 sec</t>
+          <t>12.9780 sec</t>
         </is>
       </c>
     </row>

--- a/Thesis_TSSP_NEW_M2_Results_3_Scenarios.xlsx
+++ b/Thesis_TSSP_NEW_M2_Results_3_Scenarios.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -483,12 +483,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4/5/2026 10:48</t>
+          <t>4/5/2026 10:59</t>
         </is>
       </c>
     </row>
@@ -500,17 +500,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4/5/2026 11:34</t>
+          <t>4/5/2026 15:14</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -520,12 +520,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/5/2026 12:24</t>
+          <t>4/5/2026 12:14</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -547,22 +547,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4/5/2026 06:14</t>
+          <t>4/5/2026 07:29</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/5/2026 12:02</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -584,17 +584,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4/5/2026 10:24</t>
+          <t>4/5/2026 13:29</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4/5/2026 15:14</t>
+          <t>4/5/2026 11:01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4/5/2026 15:03</t>
+          <t>4/5/2026 12:30</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:25</t>
         </is>
       </c>
     </row>
@@ -648,22 +648,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4/5/2026 08:16</t>
+          <t>4/5/2026 15:14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4/5/2026 12:25</t>
+          <t>4/5/2026 11:41</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:43</t>
+          <t>4/5/2026 07:53</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4/5/2026 15:09</t>
+          <t>4/5/2026 08:04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4/5/2026 14:31</t>
+          <t>4/5/2026 11:35</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:04</t>
+          <t>4/5/2026 07:05</t>
         </is>
       </c>
     </row>
@@ -722,27 +722,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4/5/2026 14:01</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4/5/2026 10:09</t>
+          <t>4/5/2026 15:14</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -759,32 +759,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4/5/2026 13:59</t>
+          <t>4/5/2026 08:27</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4/5/2026 15:12</t>
+          <t>4/5/2026 10:37</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4/5/2026 12:23</t>
+          <t>4/5/2026 12:49</t>
         </is>
       </c>
     </row>
@@ -796,22 +796,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4/5/2026 14:08</t>
+          <t>4/5/2026 09:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:26</t>
+          <t>4/5/2026 12:43</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4/5/2026 15:09</t>
+          <t>4/5/2026 15:14</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4/5/2026 11:59</t>
+          <t>4/5/2026 11:45</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4/5/2026 11:59</t>
+          <t>4/5/2026 12:00</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:13</t>
+          <t>4/5/2026 12:08</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4/5/2026 15:12</t>
+          <t>4/5/2026 11:18</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:42</t>
+          <t>4/5/2026 11:36</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4/5/2026 10:19</t>
+          <t>4/5/2026 08:43</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4/5/2026 12:52</t>
+          <t>4/5/2026 12:17</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -949,22 +949,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4/5/2026 07:11</t>
+          <t>4/5/2026 15:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4/5/2026 12:49</t>
+          <t>4/5/2026 13:49</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4/5/2026 09:53</t>
+          <t>4/5/2026 12:35</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4/5/2026 14:48</t>
+          <t>4/5/2026 13:12</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4/5/2026 10:31</t>
+          <t>4/5/2026 15:14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1033,17 +1033,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4/5/2026 14:47</t>
+          <t>4/5/2026 13:43</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4/5/2026 14:49</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4/5/2026 14:40</t>
+          <t>4/5/2026 15:07</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4/5/2026 12:41</t>
+          <t>4/5/2026 10:54</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4/5/2026 11:44</t>
+          <t>4/5/2026 14:37</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:50</t>
+          <t>4/5/2026 09:54</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4/5/2026 10:59</t>
+          <t>4/5/2026 11:05</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4/5/2026 12:25</t>
+          <t>4/5/2026 11:34</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4/5/2026 10:44</t>
+          <t>4/5/2026 10:35</t>
         </is>
       </c>
     </row>
@@ -1171,27 +1171,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4/5/2026 13:12</t>
+          <t>4/5/2026 15:12</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4/5/2026 10:09</t>
+          <t>4/5/2026 08:34</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4/5/2026 10:16</t>
+          <t>4/5/2026 10:31</t>
         </is>
       </c>
     </row>
@@ -1203,32 +1203,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4/5/2026 10:32</t>
+          <t>4/5/2026 11:40</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4/5/2026 14:53</t>
+          <t>4/5/2026 11:57</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40.75 min</t>
+          <t>41.70 min</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>93.00 min</t>
+          <t>87.33 min</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>96.00 min</t>
+          <t>91.00 min</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>332505 / 18309</t>
+          <t>332507 / 18351</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12.9780 sec</t>
+          <t>14.9670 sec</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.9963 %</t>
+          <t>1.9598 %</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>38.00 min | 88.00 min</t>
+          <t>39.38 min | 86.00 min</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>42.00 min | 95.00 min</t>
+          <t>42.67 min | 91.00 min</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>42.24 min | 96.00 min</t>
+          <t>43.05 min | 85.00 min</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16.52</v>
+        <v>21.24</v>
       </c>
     </row>
     <row r="34">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4.72</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="35">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>14.16</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="36">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>14.16</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="37">
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4.14</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="38">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="39">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.22</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="40">
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29.3</v>
+        <v>41.86</v>
       </c>
     </row>
     <row r="41">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>33.49</v>
+        <v>20.93</v>
       </c>
     </row>
   </sheetData>
@@ -1748,48 +1748,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4/5/2026 10:39</t>
+          <t>4/5/2026 10:40</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4/5/2026 10:47</t>
+          <t>4/5/2026 10:48</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4/5/2026 10:47</t>
+          <t>4/5/2026 10:50</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4/5/2026 10:49</t>
+          <t>4/5/2026 10:52</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4/5/2026 10:49</t>
+          <t>4/5/2026 10:59</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4/5/2026 11:19</t>
+          <t>4/5/2026 11:29</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -1834,22 +1834,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4/5/2026 12:16</t>
+          <t>4/5/2026 12:14</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4/5/2026 13:02</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1988,48 +1988,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="L6" t="n">
         <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -2048,48 +2048,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:19</t>
+          <t>4/5/2026 07:29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:39</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:36</t>
+          <t>4/5/2026 07:41</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:38</t>
+          <t>4/5/2026 07:43</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:43</t>
+          <t>4/5/2026 07:53</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:59</t>
+          <t>4/5/2026 08:09</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="N7" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -2134,22 +2134,22 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:04</t>
+          <t>4/5/2026 07:05</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:27</t>
+          <t>4/5/2026 07:28</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -2348,48 +2348,48 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4/5/2026 11:45</t>
+          <t>4/5/2026 11:41</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4/5/2026 11:54</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4/5/2026 11:57</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>4/5/2026 11:51</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>4/5/2026 11:58</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>4/5/2026 12:05</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4/5/2026 12:11</t>
+          <t>4/5/2026 12:04</t>
         </is>
       </c>
       <c r="L12" t="n">
         <v>7</v>
       </c>
       <c r="M12" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="N12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -2408,48 +2408,48 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>4/5/2026 11:14</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>4/5/2026 11:23</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:32</t>
-        </is>
-      </c>
       <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4/5/2026 11:24</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4/5/2026 11:26</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>4/5/2026 11:36</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>4/5/2026 11:56</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
         <v>10</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:34</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:36</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:42</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>4/5/2026 12:02</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>6</v>
-      </c>
       <c r="M13" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="N13" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -2541,29 +2541,29 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:24</t>
+          <t>4/5/2026 06:20</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>4/5/2026 06:22</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>4/5/2026 06:26</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>4/5/2026 06:26</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>4/5/2026 06:28</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
         <v>12</v>
@@ -2648,48 +2648,48 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:37</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:39</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:40</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:36</t>
+          <t>4/5/2026 09:49</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
@@ -2734,22 +2734,22 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:47</t>
+          <t>4/5/2026 09:38</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="N18" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -2768,48 +2768,48 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:36</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:46</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:49</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>2</v>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:37</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:40</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1</v>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:50</t>
+          <t>4/5/2026 09:54</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>4/5/2026 10:10</t>
+          <t>4/5/2026 10:14</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="N19" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -2961,35 +2961,35 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>4/5/2026 09:03</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>4/5/2026 09:05</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:07</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -3068,25 +3068,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4/5/2026 11:44</t>
+          <t>4/5/2026 11:36</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4/5/2026 12:12</t>
+          <t>4/5/2026 12:04</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>4/5/2026 12:19</t>
+          <t>4/5/2026 12:11</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4/5/2026 12:21</t>
+          <t>4/5/2026 12:13</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -3094,22 +3094,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>4/5/2026 12:23</t>
+          <t>4/5/2026 12:14</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>4/5/2026 13:09</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="N24" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
@@ -3248,25 +3248,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -3274,22 +3274,22 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -3308,48 +3308,48 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4/5/2026 07:19</t>
+          <t>4/5/2026 07:28</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>4/5/2026 07:28</t>
+          <t>4/5/2026 07:37</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:43</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4/5/2026 07:33</t>
+          <t>4/5/2026 07:45</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>4/5/2026 07:43</t>
+          <t>4/5/2026 07:53</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>4/5/2026 07:59</t>
+          <t>4/5/2026 08:09</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M28" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="N28" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
@@ -3381,35 +3381,35 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>4/5/2026 06:59</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>4/5/2026 07:01</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>4/5/2026 07:03</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4/5/2026 07:03</t>
+          <t>4/5/2026 07:05</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>4/5/2026 07:26</t>
+          <t>4/5/2026 07:28</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M29" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -3488,25 +3488,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4/5/2026 12:41</t>
+          <t>4/5/2026 12:42</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4/5/2026 12:46</t>
+          <t>4/5/2026 12:47</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4/5/2026 12:46</t>
+          <t>4/5/2026 12:47</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4/5/2026 12:48</t>
+          <t>4/5/2026 12:49</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -3514,22 +3514,22 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4/5/2026 12:48</t>
+          <t>4/5/2026 12:49</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>4/5/2026 13:17</t>
+          <t>4/5/2026 13:18</t>
         </is>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -3608,48 +3608,48 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:42</t>
+          <t>4/5/2026 11:41</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>4/5/2026 11:53</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>4/5/2026 11:53</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>4/5/2026 11:54</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:54</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:55</t>
-        </is>
-      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:57</t>
+          <t>4/5/2026 11:59</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4/5/2026 12:03</t>
+          <t>4/5/2026 12:05</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M33" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -3668,48 +3668,48 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4/5/2026 11:14</t>
+          <t>4/5/2026 11:22</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>4/5/2026 11:24</t>
+          <t>4/5/2026 11:32</t>
         </is>
       </c>
       <c r="F34" t="n">
+        <v>9</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>4/5/2026 11:33</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>4/5/2026 11:35</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>1</v>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:31</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:33</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>7</v>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>4/5/2026 11:42</t>
+          <t>4/5/2026 11:35</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>4/5/2026 12:02</t>
+          <t>4/5/2026 11:55</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="N34" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
@@ -3801,35 +3801,35 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4/5/2026 06:24</t>
+          <t>4/5/2026 06:19</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4/5/2026 06:26</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>4/5/2026 06:27</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>4/5/2026 06:29</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
         <v>6</v>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>4/5/2026 06:26</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>4/5/2026 06:28</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -3848,16 +3848,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:14</t>
+          <t>4/5/2026 07:16</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -3908,48 +3908,48 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:28</t>
+          <t>4/5/2026 09:40</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:49</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M38" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="N38" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39">
@@ -3981,35 +3981,35 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4/5/2026 09:28</t>
+          <t>4/5/2026 09:27</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
+          <t>4/5/2026 09:29</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>6</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
           <t>4/5/2026 09:30</t>
         </is>
       </c>
-      <c r="I39" t="n">
-        <v>7</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:40</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>4/5/2026 09:48</t>
+          <t>4/5/2026 09:38</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="N39" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40">
@@ -4028,48 +4028,48 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:47</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:40</t>
+          <t>4/5/2026 09:49</t>
         </is>
       </c>
       <c r="I40" t="n">
+        <v>4</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:54</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>4/5/2026 10:14</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
         <v>5</v>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:50</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>4/5/2026 10:10</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>10</v>
-      </c>
       <c r="M40" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="N40" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
@@ -4208,48 +4208,48 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="L43" t="n">
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N43" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
@@ -4341,35 +4341,35 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
+          <t>4/5/2026 12:11</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>4/5/2026 12:13</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>4/5/2026 12:15</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>4/5/2026 12:24</t>
+          <t>4/5/2026 12:13</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>4/5/2026 13:10</t>
+          <t>4/5/2026 12:59</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="N45" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4414,22 +4414,22 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>4/5/2026 13:01</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>4/5/2026 13:08</t>
+          <t>4/5/2026 13:09</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -4508,48 +4508,48 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M48" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49">
@@ -4568,48 +4568,48 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>4/5/2026 07:19</t>
+          <t>4/5/2026 07:29</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:39</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4/5/2026 07:33</t>
+          <t>4/5/2026 07:48</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>4/5/2026 07:43</t>
+          <t>4/5/2026 07:53</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>4/5/2026 07:59</t>
+          <t>4/5/2026 08:09</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M49" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="N49" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50">
@@ -4628,25 +4628,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4/5/2026 06:50</t>
+          <t>4/5/2026 06:48</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>4/5/2026 07:00</t>
+          <t>4/5/2026 06:58</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
+          <t>4/5/2026 07:05</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>4/5/2026 07:07</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>4/5/2026 07:09</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -4654,22 +4654,22 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>4/5/2026 07:19</t>
+          <t>4/5/2026 07:07</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>4/5/2026 07:42</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N50" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
@@ -4868,48 +4868,48 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4/5/2026 11:43</t>
+          <t>4/5/2026 11:41</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t>4/5/2026 11:49</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>4/5/2026 11:50</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
           <t>4/5/2026 11:51</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>2</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:58</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:59</t>
-        </is>
-      </c>
       <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>4/5/2026 11:57</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>4/5/2026 12:03</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>6</v>
+      </c>
+      <c r="M54" t="n">
+        <v>22</v>
+      </c>
+      <c r="N54" t="n">
         <v>7</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:59</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>4/5/2026 12:05</t>
-        </is>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>24</v>
-      </c>
-      <c r="N54" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="55">
@@ -4928,25 +4928,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>4/5/2026 11:13</t>
+          <t>4/5/2026 11:17</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>4/5/2026 11:23</t>
+          <t>4/5/2026 11:27</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>4/5/2026 11:29</t>
+          <t>4/5/2026 11:33</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4/5/2026 11:32</t>
+          <t>4/5/2026 11:36</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -4954,22 +4954,22 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>4/5/2026 11:42</t>
+          <t>4/5/2026 11:36</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>4/5/2026 12:02</t>
+          <t>4/5/2026 11:56</t>
         </is>
       </c>
       <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>43</v>
+      </c>
+      <c r="N55" t="n">
         <v>10</v>
-      </c>
-      <c r="M55" t="n">
-        <v>49</v>
-      </c>
-      <c r="N55" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="56">
@@ -5061,35 +5061,35 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>4/5/2026 06:19</t>
+          <t>4/5/2026 06:25</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>4/5/2026 06:22</t>
+          <t>4/5/2026 06:28</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>4/5/2026 06:26</t>
+          <t>4/5/2026 06:28</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>4/5/2026 06:28</t>
+          <t>4/5/2026 06:30</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
@@ -5168,48 +5168,48 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:28</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:51</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M59" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="N59" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60">
@@ -5228,48 +5228,48 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:28</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:40</t>
+          <t>4/5/2026 09:25</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:48</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M60" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="N60" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61">
@@ -5288,48 +5288,48 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>4/5/2026 09:44</t>
+          <t>4/5/2026 09:45</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
+          <t>4/5/2026 09:46</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
           <t>4/5/2026 09:48</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:50</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>4/5/2026 09:51</t>
+          <t>4/5/2026 09:54</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>4/5/2026 10:11</t>
+          <t>4/5/2026 10:14</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M61" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="N61" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62">
@@ -5361,35 +5361,35 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>4/5/2026 10:30</t>
+          <t>4/5/2026 10:23</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>4/5/2026 10:33</t>
+          <t>4/5/2026 10:26</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>4/5/2026 10:42</t>
+          <t>4/5/2026 10:35</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>4/5/2026 11:09</t>
+          <t>4/5/2026 11:02</t>
         </is>
       </c>
       <c r="L62" t="n">
         <v>9</v>
       </c>
       <c r="M62" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="N62" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63">
@@ -5408,48 +5408,48 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>4/5/2026 10:01</t>
+          <t>4/5/2026 10:07</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>4/5/2026 10:14</t>
+          <t>4/5/2026 10:20</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>4/5/2026 10:14</t>
+          <t>4/5/2026 10:21</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>4/5/2026 10:16</t>
+          <t>4/5/2026 10:23</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>4/5/2026 10:16</t>
+          <t>4/5/2026 10:31</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>4/5/2026 10:40</t>
+          <t>4/5/2026 10:55</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M63" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64">
@@ -5468,48 +5468,48 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>4/5/2026 08:58</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M64" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
